--- a/output/roomself_excel/13346.xlsx
+++ b/output/roomself_excel/13346.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>47433</v>
+        <v>82296</v>
       </c>
       <c r="D2" t="n">
-        <v>1816</v>
+        <v>2388</v>
       </c>
       <c r="E2" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>493</v>
+        <v>237765</v>
       </c>
       <c r="D3" t="n">
-        <v>184</v>
+        <v>4072</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>69616</v>
+        <v>47433</v>
       </c>
       <c r="D4" t="n">
-        <v>2444</v>
+        <v>1816</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="F4" t="n">
-        <v>216</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>237765</v>
+        <v>69616</v>
       </c>
       <c r="D5" t="n">
-        <v>4072</v>
+        <v>2444</v>
       </c>
       <c r="E5" t="n">
-        <v>655</v>
+        <v>238</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -554,14 +554,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1292</v>
+        <v>116184</v>
       </c>
       <c r="D6" t="n">
-        <v>372</v>
+        <v>2740</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -576,14 +576,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2703</v>
+        <v>27360</v>
       </c>
       <c r="D7" t="n">
-        <v>704</v>
+        <v>1328</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -598,14 +598,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>408</v>
+        <v>70241</v>
       </c>
       <c r="D8" t="n">
-        <v>164</v>
+        <v>3068</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>82296</v>
+        <v>8858</v>
       </c>
       <c r="D9" t="n">
-        <v>2388</v>
+        <v>756</v>
       </c>
       <c r="E9" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8858</v>
+        <v>23584</v>
       </c>
       <c r="D10" t="n">
-        <v>756</v>
+        <v>1288</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>70241</v>
+        <v>493</v>
       </c>
       <c r="D11" t="n">
-        <v>3068</v>
+        <v>184</v>
       </c>
       <c r="E11" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>116184</v>
+        <v>1292</v>
       </c>
       <c r="D12" t="n">
-        <v>2740</v>
+        <v>372</v>
       </c>
       <c r="E12" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23584</v>
+        <v>2703</v>
       </c>
       <c r="D13" t="n">
-        <v>1288</v>
+        <v>704</v>
       </c>
       <c r="E13" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27360</v>
+        <v>408</v>
       </c>
       <c r="D14" t="n">
-        <v>1328</v>
+        <v>164</v>
       </c>
       <c r="E14" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/13346.xlsx
+++ b/output/roomself_excel/13346.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,16 +449,6 @@
           <t>Perimeter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallLength</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallWidth</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -475,12 +465,6 @@
       <c r="D2" t="n">
         <v>2388</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +481,6 @@
       <c r="D3" t="n">
         <v>4072</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +497,6 @@
       <c r="D4" t="n">
         <v>1816</v>
       </c>
-      <c r="E4" t="n">
-        <v>238</v>
-      </c>
-      <c r="F4" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +513,6 @@
       <c r="D5" t="n">
         <v>2444</v>
       </c>
-      <c r="E5" t="n">
-        <v>238</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +529,6 @@
       <c r="D6" t="n">
         <v>2740</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +545,6 @@
       <c r="D7" t="n">
         <v>1328</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +561,6 @@
       <c r="D8" t="n">
         <v>3068</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +577,6 @@
       <c r="D9" t="n">
         <v>756</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +593,6 @@
       <c r="D10" t="n">
         <v>1288</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +609,6 @@
       <c r="D11" t="n">
         <v>184</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +625,6 @@
       <c r="D12" t="n">
         <v>372</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +641,6 @@
       <c r="D13" t="n">
         <v>704</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -738,12 +656,6 @@
       </c>
       <c r="D14" t="n">
         <v>164</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
